--- a/output/pdf_financials_xlsx/SQG.xlsx
+++ b/output/pdf_financials_xlsx/SQG.xlsx
@@ -6140,7 +6140,7 @@
         <v>0.683547</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>-0.008855</v>
+        <v>-0.692402</v>
       </c>
       <c r="I91" s="3" t="n">
         <v>0</v>
@@ -6198,7 +6198,7 @@
         <v>0.400427</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0.400427</v>
+        <v>0.7990080000000001</v>
       </c>
       <c r="H92" s="3" t="n">
         <v>0.00355</v>
@@ -6228,13 +6228,13 @@
         <v>1.558667</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>1.558667</v>
+        <v>-0.121621</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>-0.121621</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>-0.121621</v>
       </c>
     </row>
     <row r="93">
@@ -11954,7 +11954,11 @@
           <t>Reserve</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -82047,7 +82051,7 @@
         <v>-0.913757</v>
       </c>
       <c r="J696" s="5" t="n">
-        <v>1.876755</v>
+        <v>-1.876755</v>
       </c>
       <c r="K696" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/SQG.xlsx
+++ b/output/pdf_financials_xlsx/SQG.xlsx
@@ -955,31 +955,31 @@
         <v>0.863147</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>9.532370999999999</v>
+        <v>3.249654</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>1.492181</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>0.677376</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>0.545035</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0</v>
+        <v>0.278327</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0</v>
+        <v>0.270361</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0</v>
+        <v>0.220266</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0</v>
+        <v>0.25212</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0</v>
+        <v>0.307146</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>0.037943</v>
@@ -1016,31 +1016,31 @@
         <v>2.528906</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>13.587643</v>
+        <v>19.87036</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0</v>
+        <v>-1.492181</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0</v>
+        <v>-0.677376</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0</v>
+        <v>-0.545035</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0</v>
+        <v>-0.278327</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0</v>
+        <v>-0.270361</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0</v>
+        <v>-0.220266</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>0</v>
+        <v>-0.25212</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0</v>
+        <v>-0.307146</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>0.945647</v>
@@ -2525,19 +2525,19 @@
         <v>0.404534</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.101819</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.095342</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.083221</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.07299600000000001</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.00747</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>2.59628</v>
@@ -2647,19 +2647,19 @@
         <v>0.404534</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.101819</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.095342</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.083221</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.07299600000000001</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.00747</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>2.59628</v>
@@ -3379,7 +3379,7 @@
         <v>13.990933</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>4.063959</v>
+        <v>3.96214</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0</v>
@@ -13210,7 +13210,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -22552,7 +22552,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -25574,7 +25574,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -76308,7 +76308,7 @@
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
@@ -78004,7 +78004,7 @@
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">

--- a/output/pdf_financials_xlsx/SQG.xlsx
+++ b/output/pdf_financials_xlsx/SQG.xlsx
@@ -2196,13 +2196,13 @@
         <v>0</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0.152047</v>
+        <v>0.169465</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0.15569</v>
+        <v>0.186774</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>0.155238</v>
+        <v>0.198677</v>
       </c>
     </row>
     <row r="29">
@@ -2257,13 +2257,13 @@
         <v>-0.433467</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>1.06758</v>
+        <v>1.084998</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-2.51366</v>
+        <v>-2.482576</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-0.320517</v>
+        <v>-0.277078</v>
       </c>
     </row>
     <row r="30">
@@ -2334,13 +2334,13 @@
         </is>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>7.559936599014258</v>
+        <v>7.68328002590651</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-44.51015035983019</v>
+        <v>-43.95973641610473</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>-4.10888098094106</v>
+        <v>-3.552012917995572</v>
       </c>
     </row>
     <row r="31">
@@ -6668,13 +6668,13 @@
         <v>0</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>0.404707</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>0.348763</v>
       </c>
       <c r="S100" s="3" t="n">
-        <v>0</v>
+        <v>0.314307</v>
       </c>
     </row>
     <row r="101">
@@ -7367,10 +7367,10 @@
         <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.497924</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.020202</v>
       </c>
       <c r="H112" s="3" t="n">
         <v>0</v>
@@ -7400,13 +7400,13 @@
         <v>0</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>0</v>
+        <v>0.026795</v>
       </c>
       <c r="R112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S112" s="3" t="n">
-        <v>0</v>
+        <v>0.007704</v>
       </c>
     </row>
     <row r="113">
@@ -38650,7 +38650,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -38966,7 +38970,11 @@
           <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>
@@ -39070,7 +39078,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -41446,7 +41454,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
           <t>-</t>
@@ -43634,7 +43646,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D330" t="inlineStr"/>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E330" t="inlineStr">
         <is>
           <t>-</t>
@@ -44456,7 +44472,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr"/>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr">
         <is>
           <t>-</t>
@@ -57222,7 +57242,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D460" t="inlineStr"/>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E460" t="inlineStr">
         <is>
           <t>-</t>
@@ -67054,7 +67078,11 @@
           <t>Depreciation of property and equipment 11</t>
         </is>
       </c>
-      <c r="D553" t="inlineStr"/>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E553" t="inlineStr">
         <is>
           <t>-</t>
@@ -67262,7 +67290,7 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
@@ -68810,7 +68838,11 @@
           <t>Depreciation of property, plant and equipment 11</t>
         </is>
       </c>
-      <c r="D570" t="inlineStr"/>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E570" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SQG.xlsx
+++ b/output/pdf_financials_xlsx/SQG.xlsx
@@ -1625,10 +1625,10 @@
         <v>-0.174649</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>-0.199544</v>
+        <v>-0.256664</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>-0.60791</v>
+        <v>-0.313891</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>-0.913757</v>
@@ -1689,7 +1689,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0</v>
+        <v>-0.294019</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>0</v>
@@ -2723,13 +2723,13 @@
         <v>0</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>0</v>
+        <v>0.259048</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>0</v>
+        <v>0.291353</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>0</v>
+        <v>0.52184</v>
       </c>
     </row>
     <row r="38">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.442446</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>0.024016</v>
@@ -2909,10 +2909,10 @@
         <v>0.023267</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>0</v>
+        <v>0.002759</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>0</v>
+        <v>0.002701</v>
       </c>
     </row>
     <row r="41">
@@ -2934,7 +2934,7 @@
         <v>0.045631</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>4.20798</v>
+        <v>4.650426</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>3.269975</v>
@@ -2967,13 +2967,13 @@
         <v>0</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>0.023267</v>
+        <v>0.282315</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>0</v>
+        <v>0.294112</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>0</v>
+        <v>0.524541</v>
       </c>
     </row>
     <row r="42">
@@ -3394,13 +3394,13 @@
         <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>5.155384</v>
+        <v>4.896336</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>3.612097</v>
+        <v>3.317985</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>5.179776</v>
+        <v>4.655235</v>
       </c>
     </row>
     <row r="49">
@@ -4596,46 +4596,46 @@
         <v>0</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.241074</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.075846</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.09890699999999999</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.1255</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.182676</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.21396</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.303427</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>0.44301</v>
       </c>
       <c r="S67" s="3" t="n">
-        <v>0</v>
+        <v>0.406002</v>
       </c>
     </row>
     <row r="68">
@@ -4693,10 +4693,10 @@
         <v>0.424425</v>
       </c>
       <c r="R68" s="3" t="n">
-        <v>2.598107</v>
+        <v>3.041117</v>
       </c>
       <c r="S68" s="3" t="n">
-        <v>4.200651</v>
+        <v>4.606653</v>
       </c>
     </row>
     <row r="69">
@@ -5120,10 +5120,10 @@
         <v>2.971382</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>0.385513</v>
+        <v>0</v>
       </c>
       <c r="S75" s="3" t="n">
-        <v>0.921076</v>
+        <v>0.515074</v>
       </c>
     </row>
     <row r="76">
@@ -6568,10 +6568,10 @@
         <v>-0.174649</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>-0.199544</v>
+        <v>-0.256664</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>-0.60791</v>
+        <v>-0.313891</v>
       </c>
       <c r="F99" s="3" t="n">
         <v>-0.913757</v>
@@ -7162,7 +7162,7 @@
         <v>0</v>
       </c>
       <c r="S108" s="3" t="n">
-        <v>0</v>
+        <v>0.01266</v>
       </c>
     </row>
     <row r="109">
@@ -7272,19 +7272,19 @@
         <v>0</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.003883</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>0.016516</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>0.031689</v>
       </c>
       <c r="R110" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S110" s="3" t="n">
-        <v>0</v>
+        <v>0.008324</v>
       </c>
     </row>
     <row r="111">
@@ -7489,7 +7489,7 @@
         <v>0</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>0</v>
+        <v>-3.907193</v>
       </c>
       <c r="G114" s="3" t="n">
         <v>0</v>
@@ -7547,10 +7547,10 @@
         <v>0</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.15569</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>2.788859</v>
       </c>
       <c r="G115" s="3" t="n">
         <v>0</v>
@@ -38236,7 +38236,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E278" t="inlineStr">
         <is>
           <t>-</t>
@@ -39498,7 +39502,11 @@
           <t>Impairment loss on goodwill 15</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E290" t="inlineStr">
         <is>
           <t>-</t>
@@ -48288,7 +48296,11 @@
           <t>607,583 Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D375" t="inlineStr"/>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E375" t="inlineStr">
         <is>
           <t>-</t>
@@ -49444,7 +49456,11 @@
           <t>Deferred income tax recovery 607,583</t>
         </is>
       </c>
-      <c r="D386" t="inlineStr"/>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E386" t="inlineStr">
         <is>
           <t>-</t>
@@ -54404,7 +54420,11 @@
           <t>Deferred income tax expense (Note 14)</t>
         </is>
       </c>
-      <c r="D433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E433" t="inlineStr">
         <is>
           <t>-</t>
@@ -55150,7 +55170,11 @@
           <t>Net profit (loss) from continuing operations $</t>
         </is>
       </c>
-      <c r="D440" t="inlineStr"/>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E440" t="inlineStr">
         <is>
           <t>-</t>
@@ -55175,7 +55199,7 @@
         <v>-0.913757</v>
       </c>
       <c r="J440" s="5" t="n">
-        <v>1.876755</v>
+        <v>-1.876755</v>
       </c>
       <c r="K440" t="inlineStr">
         <is>
@@ -59444,7 +59468,11 @@
           <t>Net loss from continuing operations $</t>
         </is>
       </c>
-      <c r="D481" t="inlineStr"/>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E481" t="inlineStr">
         <is>
           <t>-</t>
@@ -60184,7 +60212,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D488" t="inlineStr"/>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E488" t="inlineStr">
         <is>
           <t>-</t>
@@ -60290,7 +60322,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D489" t="inlineStr"/>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E489" t="inlineStr">
         <is>
           <t>-</t>
@@ -74228,7 +74264,11 @@
           <t>Deferred income tax recovery 13</t>
         </is>
       </c>
-      <c r="D622" t="inlineStr"/>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E622" t="inlineStr">
         <is>
           <t>-</t>
@@ -75176,7 +75216,11 @@
           <t>Deferred income tax (recovery) expense 12</t>
         </is>
       </c>
-      <c r="D631" t="inlineStr"/>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E631" t="inlineStr">
         <is>
           <t>-</t>
@@ -76554,7 +76598,11 @@
           <t>Deferred income tax (recovery) expense 14</t>
         </is>
       </c>
-      <c r="D644" t="inlineStr"/>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E644" t="inlineStr">
         <is>
           <t>-</t>
@@ -83104,7 +83152,11 @@
           <t>Income tax recovery (Note 25)</t>
         </is>
       </c>
-      <c r="D706" t="inlineStr"/>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E706" t="inlineStr">
         <is>
           <t>-</t>
@@ -83210,7 +83262,11 @@
           <t>Loss from continuing operation</t>
         </is>
       </c>
-      <c r="D707" t="inlineStr"/>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E707" t="inlineStr">
         <is>
           <t>-</t>
@@ -83314,7 +83370,11 @@
           <t>Loss from discontinued operations (Note 5)</t>
         </is>
       </c>
-      <c r="D708" t="inlineStr"/>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E708" t="inlineStr">
         <is>
           <t>-</t>
@@ -84054,7 +84114,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D715" t="inlineStr"/>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E715" t="inlineStr">
         <is>
           <t>-</t>
